--- a/data/trans_orig/P17E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2007</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47464</t>
+          <t>47416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60041</t>
+          <t>60402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74910</t>
+          <t>75102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99820</t>
+          <t>98012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119241</t>
+          <t>118845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>24931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>32829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>55648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47218</t>
+          <t>47886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>75576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62492</t>
+          <t>62779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95029</t>
+          <t>94922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116842</t>
+          <t>117741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148601</t>
+          <t>147844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176202</t>
+          <t>175534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>31219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32149</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>54357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51547</t>
+          <t>50672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79394</t>
+          <t>79546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62634</t>
+          <t>63393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79747</t>
+          <t>79690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131031</t>
+          <t>131277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153485</t>
+          <t>153834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>200852</t>
+          <t>200700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>228699</t>
+          <t>229574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30621</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52671</t>
+          <t>53466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50046</t>
+          <t>50953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>77371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50657</t>
+          <t>50327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66898</t>
+          <t>66676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94793</t>
+          <t>93998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116843</t>
+          <t>116387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152063</t>
+          <t>151526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178851</t>
+          <t>177944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>26870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47577</t>
+          <t>47273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43353</t>
+          <t>41918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71979</t>
+          <t>68168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101194</t>
+          <t>99360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114848</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>102973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>123627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>204497</t>
+          <t>208308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233123</t>
+          <t>234558</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33257</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58412</t>
+          <t>59627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96885</t>
+          <t>96006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115990</t>
+          <t>115490</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133831</t>
+          <t>134738</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150218</t>
+          <t>150243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237847</t>
+          <t>236632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263002</t>
+          <t>261365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76026</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>87810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146499</t>
+          <t>148228</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>162366</t>
+          <t>162515</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228534</t>
+          <t>229186</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>247797</t>
+          <t>247976</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112176</t>
+          <t>110379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>151915</t>
+          <t>151942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>182290</t>
+          <t>186456</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238856</t>
+          <t>238596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>307022</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>375223</t>
+          <t>373086</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>507387</t>
+          <t>507360</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>547126</t>
+          <t>548923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>809514</t>
+          <t>809774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>866080</t>
+          <t>861914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1332449</t>
+          <t>1334586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1398368</t>
+          <t>1400650</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2012</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2012 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>30911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>43564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55829</t>
+          <t>55178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67905</t>
+          <t>67319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83672</t>
+          <t>84326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117574</t>
+          <t>116329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136670</t>
+          <t>136572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14864</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>31970</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23865</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46296</t>
+          <t>47090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44710</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72146</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67603</t>
+          <t>68295</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85401</t>
+          <t>85771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117790</t>
+          <t>116996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140221</t>
+          <t>139173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>192205</t>
+          <t>191625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219641</t>
+          <t>220142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54665</t>
+          <t>53766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53629</t>
+          <t>54616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83980</t>
+          <t>85369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91195</t>
+          <t>91118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111008</t>
+          <t>110343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139027</t>
+          <t>139926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162280</t>
+          <t>162132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238095</t>
+          <t>236706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>268446</t>
+          <t>267459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>41916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73866</t>
+          <t>74168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74208</t>
+          <t>74379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93666</t>
+          <t>93616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151097</t>
+          <t>151626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172550</t>
+          <t>172433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233411</t>
+          <t>233109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261798</t>
+          <t>262065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36301</t>
+          <t>35857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42801</t>
+          <t>42354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43001</t>
+          <t>43601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71502</t>
+          <t>70965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92969</t>
+          <t>93413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112039</t>
+          <t>112030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117846</t>
+          <t>118293</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138987</t>
+          <t>138642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218414</t>
+          <t>218951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246915</t>
+          <t>246315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>24464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45415</t>
+          <t>44771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21170</t>
+          <t>21602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50203</t>
+          <t>51578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79645</t>
+          <t>80380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89850</t>
+          <t>90494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>110801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112539</t>
+          <t>113117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132653</t>
+          <t>132221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209442</t>
+          <t>208707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>238884</t>
+          <t>237509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>28301</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>34849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30639</t>
+          <t>29811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87836</t>
+          <t>85979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104330</t>
+          <t>103467</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>156193</t>
+          <t>154595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174166</t>
+          <t>174265</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248138</t>
+          <t>248586</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273084</t>
+          <t>273912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139462</t>
+          <t>141433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>187798</t>
+          <t>187992</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187618</t>
+          <t>188703</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>240049</t>
+          <t>241434</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>341123</t>
+          <t>341360</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>415989</t>
+          <t>409593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>592342</t>
+          <t>592148</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>640678</t>
+          <t>638707</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>913415</t>
+          <t>912030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>965846</t>
+          <t>964761</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1517615</t>
+          <t>1524011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1592481</t>
+          <t>1592244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2016</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27439</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50016</t>
+          <t>50690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62680</t>
+          <t>62369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>65241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81228</t>
+          <t>80461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120803</t>
+          <t>121277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140234</t>
+          <t>140723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>43760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>38647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65054</t>
+          <t>66369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62681</t>
+          <t>62567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79196</t>
+          <t>79591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112955</t>
+          <t>114294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134513</t>
+          <t>134282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184254</t>
+          <t>182939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208985</t>
+          <t>210661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40909</t>
+          <t>40927</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28828</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50628</t>
+          <t>51446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54804</t>
+          <t>54373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84085</t>
+          <t>84043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104175</t>
+          <t>104157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124458</t>
+          <t>124081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123329</t>
+          <t>122511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145129</t>
+          <t>144635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234957</t>
+          <t>234999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264238</t>
+          <t>264669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40382</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41879</t>
+          <t>41361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74684</t>
+          <t>75979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125957</t>
+          <t>126092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146412</t>
+          <t>147273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139906</t>
+          <t>140424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160843</t>
+          <t>160343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273440</t>
+          <t>272145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303259</t>
+          <t>302160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35042</t>
+          <t>35121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30495</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55065</t>
+          <t>57297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>51132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83357</t>
+          <t>84194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106966</t>
+          <t>106887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125346</t>
+          <t>126064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141187</t>
+          <t>138955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165757</t>
+          <t>165659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254904</t>
+          <t>254067</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286390</t>
+          <t>287129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,88%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35680</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41403</t>
+          <t>40886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44884</t>
+          <t>43836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72549</t>
+          <t>71404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95476</t>
+          <t>94707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113448</t>
+          <t>113074</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144292</t>
+          <t>144809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164509</t>
+          <t>164796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244302</t>
+          <t>245447</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>271967</t>
+          <t>273015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>40022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58321</t>
+          <t>57903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83546</t>
+          <t>82875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97231</t>
+          <t>97333</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135309</t>
+          <t>135217</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157228</t>
+          <t>157361</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>224644</t>
+          <t>225062</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250363</t>
+          <t>250601</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133518</t>
+          <t>133418</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178957</t>
+          <t>181224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>196249</t>
+          <t>193700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>251235</t>
+          <t>247380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>341478</t>
+          <t>343729</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>411442</t>
+          <t>418287</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>672677</t>
+          <t>670410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>718116</t>
+          <t>718216</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>913085</t>
+          <t>916940</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>968071</t>
+          <t>970620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1604511</t>
+          <t>1597666</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1674475</t>
+          <t>1672224</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2023</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17089</t>
+          <t>17331</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44173</t>
+          <t>42693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42097</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>68939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24508</t>
+          <t>24442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>37563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53055</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54136</t>
+          <t>54202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71601</t>
+          <t>72218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>127892</t>
+          <t>128551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161512</t>
+          <t>161967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191703</t>
+          <t>190848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>230975</t>
+          <t>232306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41820</t>
+          <t>41781</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39225</t>
+          <t>39809</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62183</t>
+          <t>61841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55636</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69805</t>
+          <t>69147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75954</t>
+          <t>75993</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92299</t>
+          <t>91250</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134892</t>
+          <t>135234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157850</t>
+          <t>157266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27613</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49731</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34690</t>
+          <t>34810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52543</t>
+          <t>53184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66920</t>
+          <t>67225</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94568</t>
+          <t>95453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76150</t>
+          <t>76647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>98971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115303</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>133036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199158</t>
+          <t>198273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226806</t>
+          <t>226501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30267</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50185</t>
+          <t>50446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>43300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62304</t>
+          <t>61834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86419</t>
+          <t>86777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88450</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108368</t>
+          <t>108603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95487</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110675</t>
+          <t>110722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190628</t>
+          <t>190270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>214743</t>
+          <t>215213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24544</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33510</t>
+          <t>33558</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>51599</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73818</t>
+          <t>74062</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87645</t>
+          <t>87335</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97853</t>
+          <t>97662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109091</t>
+          <t>108559</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175536</t>
+          <t>175560</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193649</t>
+          <t>193601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>24550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>29977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47163</t>
+          <t>47643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53310</t>
+          <t>54287</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65985</t>
+          <t>67331</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103634</t>
+          <t>103683</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115031</t>
+          <t>115073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>161467</t>
+          <t>160987</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178225</t>
+          <t>178653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132227</t>
+          <t>132158</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>174862</t>
+          <t>178224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144797</t>
+          <t>149534</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>220225</t>
+          <t>219688</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>290101</t>
+          <t>295990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>382749</t>
+          <t>383975</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>463966</t>
+          <t>460604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>506601</t>
+          <t>506670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>675612</t>
+          <t>676149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>751040</t>
+          <t>746303</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1151916</t>
+          <t>1150690</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1244564</t>
+          <t>1238675</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47416</t>
+          <t>47308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60402</t>
+          <t>60006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75102</t>
+          <t>74116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98012</t>
+          <t>98998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118845</t>
+          <t>118741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24931</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32829</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55648</t>
+          <t>55228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>74722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47918</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62779</t>
+          <t>62473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94922</t>
+          <t>95342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117741</t>
+          <t>117557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147844</t>
+          <t>148698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175534</t>
+          <t>176067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54357</t>
+          <t>55183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50672</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79546</t>
+          <t>78413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63393</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79690</t>
+          <t>79383</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131277</t>
+          <t>130451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153834</t>
+          <t>153290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>200700</t>
+          <t>201833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229574</t>
+          <t>228669</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14756</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53466</t>
+          <t>52665</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>49850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>77408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50327</t>
+          <t>50803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66676</t>
+          <t>67792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93998</t>
+          <t>94799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116387</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151526</t>
+          <t>151489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177944</t>
+          <t>179047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47273</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41918</t>
+          <t>41321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68168</t>
+          <t>67823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99360</t>
+          <t>100783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114166</t>
+          <t>115256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102973</t>
+          <t>100440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123627</t>
+          <t>122248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208308</t>
+          <t>208653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234558</t>
+          <t>235155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>37184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>26711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>34210</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59627</t>
+          <t>58823</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>96006</t>
+          <t>97738</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115490</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134738</t>
+          <t>134626</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150243</t>
+          <t>150322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>236632</t>
+          <t>237436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261365</t>
+          <t>262049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76903</t>
+          <t>76118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87810</t>
+          <t>87759</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>147489</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>162515</t>
+          <t>162506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>229186</t>
+          <t>229287</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>247976</t>
+          <t>247546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110379</t>
+          <t>111032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>151942</t>
+          <t>151224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186456</t>
+          <t>187574</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238596</t>
+          <t>237650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>307022</t>
+          <t>306808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>373086</t>
+          <t>373335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>507360</t>
+          <t>508078</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>548923</t>
+          <t>548270</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>809774</t>
+          <t>810720</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>861914</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1334586</t>
+          <t>1334337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1400650</t>
+          <t>1400864</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30911</t>
+          <t>31754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20913</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40845</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43564</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67319</t>
+          <t>66476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84326</t>
+          <t>83439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116329</t>
+          <t>116788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136572</t>
+          <t>136261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31970</t>
+          <t>32244</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47090</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72726</t>
+          <t>71310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68295</t>
+          <t>68021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85771</t>
+          <t>85647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116996</t>
+          <t>116788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139173</t>
+          <t>138746</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191625</t>
+          <t>193041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220142</t>
+          <t>219917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37264</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>31498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53766</t>
+          <t>55213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54616</t>
+          <t>53949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85369</t>
+          <t>82554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91118</t>
+          <t>91247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110343</t>
+          <t>110243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139926</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162132</t>
+          <t>162194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>236706</t>
+          <t>239521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267459</t>
+          <t>268126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>19831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>40181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45212</t>
+          <t>45439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74168</t>
+          <t>75363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74379</t>
+          <t>73554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93616</t>
+          <t>93904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151626</t>
+          <t>152622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172433</t>
+          <t>172709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233109</t>
+          <t>231914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262065</t>
+          <t>261838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>35570</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,47 +5099,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>27,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>30564</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21423</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43655</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>13,34%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>30564</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22005</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42354</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70965</t>
+          <t>70761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93413</t>
+          <t>93700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112030</t>
+          <t>111663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,49 +5212,49 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>86,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>130083</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>116992</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>139224</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>80,97%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>72,83%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>86,66%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>130083</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>118293</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>138642</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,97%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>73,64%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>86,3%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218951</t>
+          <t>219155</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246315</t>
+          <t>247204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24464</t>
+          <t>23785</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44771</t>
+          <t>46042</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51578</t>
+          <t>51852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80380</t>
+          <t>80568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90494</t>
+          <t>89223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110801</t>
+          <t>111480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113117</t>
+          <t>112323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132221</t>
+          <t>132260</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>208707</t>
+          <t>208519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237509</t>
+          <t>237235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28301</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34849</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29811</t>
+          <t>30661</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>54905</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85979</t>
+          <t>87130</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103467</t>
+          <t>103863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154595</t>
+          <t>154716</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174265</t>
+          <t>174281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248586</t>
+          <t>248818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273912</t>
+          <t>273062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141433</t>
+          <t>142425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>187992</t>
+          <t>187611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188703</t>
+          <t>188036</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241434</t>
+          <t>241797</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>341360</t>
+          <t>339911</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>409593</t>
+          <t>413673</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>592148</t>
+          <t>592529</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>638707</t>
+          <t>637715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>912030</t>
+          <t>911667</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>964761</t>
+          <t>965428</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1524011</t>
+          <t>1519931</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1592244</t>
+          <t>1593693</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40125</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50690</t>
+          <t>51047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62369</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>65972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>80617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121277</t>
+          <t>120882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140723</t>
+          <t>140389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28688</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43760</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38647</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66369</t>
+          <t>64503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62567</t>
+          <t>63442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>79018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114294</t>
+          <t>115582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134282</t>
+          <t>135775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182939</t>
+          <t>184805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210661</t>
+          <t>209905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21003</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40927</t>
+          <t>39742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51446</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54373</t>
+          <t>56466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84043</t>
+          <t>85389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104157</t>
+          <t>105342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124081</t>
+          <t>125696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122511</t>
+          <t>121830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144635</t>
+          <t>144368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234999</t>
+          <t>233653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264669</t>
+          <t>262576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>40469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41361</t>
+          <t>39838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45964</t>
+          <t>45256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75979</t>
+          <t>72971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>125870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147273</t>
+          <t>147693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140424</t>
+          <t>141947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160343</t>
+          <t>161446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>272145</t>
+          <t>275153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>302160</t>
+          <t>302868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35121</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57297</t>
+          <t>54415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>51954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84194</t>
+          <t>83497</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106887</t>
+          <t>106973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126064</t>
+          <t>125714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138955</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165659</t>
+          <t>166646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254067</t>
+          <t>254764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>287129</t>
+          <t>286307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>36131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40886</t>
+          <t>43112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71404</t>
+          <t>71329</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94707</t>
+          <t>95025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113074</t>
+          <t>113516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>144809</t>
+          <t>142583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164796</t>
+          <t>165119</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>245447</t>
+          <t>245522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273015</t>
+          <t>272784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40022</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57903</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82875</t>
+          <t>83748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97333</t>
+          <t>97724</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135217</t>
+          <t>134987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157361</t>
+          <t>156936</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225062</t>
+          <t>226399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250601</t>
+          <t>251305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133418</t>
+          <t>133344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181224</t>
+          <t>180688</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>193700</t>
+          <t>193667</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>247380</t>
+          <t>250617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>343729</t>
+          <t>341072</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>418287</t>
+          <t>415502</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>670410</t>
+          <t>670946</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>718216</t>
+          <t>718290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>916940</t>
+          <t>913703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>970620</t>
+          <t>970653</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1597666</t>
+          <t>1600451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1672224</t>
+          <t>1674881</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35439</t>
+          <t>39960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28294</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>18365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42693</t>
+          <t>46145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27932</t>
+          <t>25174</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>25153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>62222</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43577</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68939</t>
+          <t>74982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>65113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>65113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>65113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>93347</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>93347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>93347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>16448</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24442</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37563</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53910</t>
+          <t>55007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65009</t>
+          <t>65304</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54202</t>
+          <t>53674</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72218</t>
+          <t>73685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146615</t>
+          <t>86803</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128551</t>
+          <t>77319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161967</t>
+          <t>95649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>211624</t>
+          <t>152107</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190848</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>232306</t>
+          <t>164329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>81752</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>81752</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>81752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>166114</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166114</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>166114</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>244758</t>
+          <t>192536</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>244758</t>
+          <t>192536</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>244758</t>
+          <t>192536</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33616</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49898</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61841</t>
+          <t>69894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63019</t>
+          <t>71459</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54222</t>
+          <t>61800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69147</t>
+          <t>78940</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84158</t>
+          <t>96422</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75993</t>
+          <t>86547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91250</t>
+          <t>104553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>147177</t>
+          <t>167881</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135234</t>
+          <t>154498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157266</t>
+          <t>180932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79300</t>
+          <t>90643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79300</t>
+          <t>90643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79300</t>
+          <t>90643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117774</t>
+          <t>133749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117774</t>
+          <t>133749</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117774</t>
+          <t>133749</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>197075</t>
+          <t>224392</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>197075</t>
+          <t>224392</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197075</t>
+          <t>224392</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37269</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49234</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43969</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34810</t>
+          <t>40729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53184</t>
+          <t>60497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>81237</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67225</t>
+          <t>76095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95453</t>
+          <t>105565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88612</t>
+          <t>99896</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76647</t>
+          <t>85498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98971</t>
+          <t>110444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123877</t>
+          <t>128582</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114662</t>
+          <t>118044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133036</t>
+          <t>137812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>212489</t>
+          <t>228479</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198273</t>
+          <t>212604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226501</t>
+          <t>242074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>125881</t>
+          <t>139627</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>125881</t>
+          <t>139627</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125881</t>
+          <t>139627</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>167846</t>
+          <t>178541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>167846</t>
+          <t>178541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>167846</t>
+          <t>178541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>293726</t>
+          <t>318169</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>293726</t>
+          <t>318169</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>293726</t>
+          <t>318169</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39822</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50446</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34636</t>
+          <t>40692</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>49590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74457</t>
+          <t>81668</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61834</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86777</t>
+          <t>95296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>98813</t>
+          <t>101146</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88189</t>
+          <t>90359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108603</t>
+          <t>110528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>117117</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95112</t>
+          <t>108219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110722</t>
+          <t>124585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>202590</t>
+          <t>218263</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190270</t>
+          <t>204635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>215213</t>
+          <t>231841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>138635</t>
+          <t>142122</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138635</t>
+          <t>142122</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138635</t>
+          <t>142122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>277047</t>
+          <t>299931</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>277047</t>
+          <t>299931</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>277047</t>
+          <t>299931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>33780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24735</t>
+          <t>27641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42237</t>
+          <t>46056</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33558</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51599</t>
+          <t>55764</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>81167</t>
+          <t>90189</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74062</t>
+          <t>81926</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87335</t>
+          <t>96987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>103755</t>
+          <t>114743</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97662</t>
+          <t>107641</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108559</t>
+          <t>120146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>184922</t>
+          <t>204931</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175560</t>
+          <t>195223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193601</t>
+          <t>214704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>104761</t>
+          <t>115706</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104761</t>
+          <t>115706</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104761</t>
+          <t>115706</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>122397</t>
+          <t>135282</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>122397</t>
+          <t>135282</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122397</t>
+          <t>135282</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>22397</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>19228</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>41625</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29977</t>
+          <t>33542</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47643</t>
+          <t>51821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>60474</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54287</t>
+          <t>60529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67331</t>
+          <t>75128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>125326</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103683</t>
+          <t>118572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115073</t>
+          <t>131254</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>170495</t>
+          <t>192815</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>160987</t>
+          <t>182619</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178653</t>
+          <t>200898</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>128233</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>128233</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128233</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>208630</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>208630</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>208630</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>153801</t>
+          <t>167311</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132158</t>
+          <t>146418</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178224</t>
+          <t>194015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>193591</t>
+          <t>219793</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>196315</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219688</t>
+          <t>243175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>347392</t>
+          <t>387104</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>295990</t>
+          <t>355774</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>383975</t>
+          <t>422041</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>485027</t>
+          <t>520658</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>460604</t>
+          <t>493954</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>506670</t>
+          <t>541551</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>702246</t>
+          <t>706040</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>676149</t>
+          <t>682658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>746303</t>
+          <t>729518</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1187273</t>
+          <t>1226698</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1150690</t>
+          <t>1191761</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1238675</t>
+          <t>1258028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P17E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Edad-trans_orig.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2203,7 +2203,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5182,7 +5182,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6789,7 +6789,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7818,7 +7818,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -8504,7 +8504,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9768,7 +9768,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10454,7 +10454,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -11140,7 +11140,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
